--- a/MagicBricksDemo/MagicBricksDemo/target/classes/TestData/LoginData.xlsx
+++ b/MagicBricksDemo/MagicBricksDemo/target/classes/TestData/LoginData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHRDEOKA\eclipse-workspace\MagicBricksDemo\src\test\resource\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40252C1A-B257-40C2-A506-4772BBA8A2EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B3E3129-5BCC-475B-A758-4621719816AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4065" yWindow="3015" windowWidth="15375" windowHeight="7785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -362,7 +362,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>8080636715</v>
+        <v>7666317918</v>
       </c>
       <c r="B2" s="1"/>
     </row>
